--- a/feedback_forms/029_monthly_training_follow_up_form--feedback_forms.xlsx
+++ b/feedback_forms/029_monthly_training_follow_up_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>Monthly Training Follow Up Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>participant_category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Participant Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>participant_description_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Participant Description</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,40 +584,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>participant_date</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Participant Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>training_type_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Training Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>participant_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Participant Location</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>training_type</t>
+          <t>participant_comments_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>training_type</t>
+          <t>Participant Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>participant_id_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Participant ID</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>participant_email_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Participant Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>participant_phone_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Participant Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_id</t>
+          <t>training_status_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_id</t>
+          <t>Training Status</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>participant_rating_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Participant Rating</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,297 +791,67 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>rating_scale_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Rating Scale</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>follow_up_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Follow Up</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>participant_follow_up_status_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Participant Follow Up Status</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>training_status</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>training_status</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>training_status</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>training_status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>participant_comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>participant_comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>follow_up</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_rating</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>participant_rating</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>participant_rating</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>participant_rating</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rating_scale</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>rating_scale</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>rating_scale</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>rating_scale</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,7 +896,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>participant_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1136,14 +906,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>category_a</t>
+          <t>category a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>participant_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1153,14 +923,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>category_b</t>
+          <t>category b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training_type_choices</t>
+          <t>training_type_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1170,14 +940,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>training_type_a</t>
+          <t>training type a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>training_type_choices</t>
+          <t>training_type_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1187,14 +957,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>training_type_b</t>
+          <t>training type b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>participant_location_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1204,14 +974,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>location_a</t>
+          <t>location a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>participant_location_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1221,14 +991,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>location_b</t>
+          <t>location b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>participant_id_choices</t>
+          <t>participant_id_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,14 +1008,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>participant_id_a</t>
+          <t>participant id a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>participant_id_choices</t>
+          <t>participant_id_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1255,14 +1025,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>participant_id_b</t>
+          <t>participant id b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>training_status_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1272,14 +1042,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>training_status_a</t>
+          <t>training status a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>training_status_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1289,313 +1059,143 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>training_status_b</t>
+          <t>training status b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>participant_rating_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>training_status_a</t>
+          <t>rating_a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>training_status_a</t>
+          <t>rating a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>training_status_choices</t>
+          <t>participant_rating_1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>training_status_b</t>
+          <t>rating_b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>training_status_b</t>
+          <t>rating b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>participant_comments_choices</t>
+          <t>rating_scale_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_comments_a</t>
+          <t>rating_scale_a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_comments_a</t>
+          <t>rating scale a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>participant_comments_choices</t>
+          <t>rating_scale_1_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_comments_b</t>
+          <t>rating_scale_b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>participant_comments_b</t>
+          <t>rating scale b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>participant_comments_choices</t>
+          <t>follow_up_1_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>follow_up_a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>follow up a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>participant_comments_choices</t>
+          <t>follow_up_1_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>follow_up_b</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>follow up b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>participant_follow_up_status_1_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>follow_up_a</t>
+          <t>follow_up_status_a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>follow_up_a</t>
+          <t>follow up status a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>participant_follow_up_status_1_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>follow_up_b</t>
+          <t>follow_up_status_b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>follow_up_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>follow_up_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>participant_rating_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_rating_a</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>participant_rating_a</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>participant_rating_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>participant_rating_b</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>participant_rating_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>participant_rating_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>participant_rating_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>rating_scale_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>rating_scale_a</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>rating_scale_a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>rating_scale_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rating_scale_b</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>rating_scale_b</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>rating_scale_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>rating_scale_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Fair</t>
+          <t>follow up status b</t>
         </is>
       </c>
     </row>
